--- a/GWD Data/Metallic PH.xlsx
+++ b/GWD Data/Metallic PH.xlsx
@@ -1,17 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Metallic PH" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>Metallic Pump House of size 1.2 x 0.9 x 2 m</t>
   </si>
@@ -55,18 +62,20 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>m</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -83,18 +92,20 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>m</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -103,236 +114,143 @@
     <t>Providing and laying in position cement concrete of specified grade excluding the cost of centering and shuttering - All work up to plinth level: 1:4:8 as per DSR item 4.1.8</t>
   </si>
   <si>
+    <t>Coursed rubble masonry (first sort) with hard stone in foundation and plinth with Cement mortar 1:6 as per DSR item 7.6.1</t>
+  </si>
+  <si>
+    <t>Foundation &amp; Basement</t>
+  </si>
+  <si>
+    <t>12 mm cement plaster of mix 1:4 as per DSR item 13.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outside </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top </t>
+  </si>
+  <si>
+    <t>Step sides</t>
+  </si>
+  <si>
+    <t>Step top</t>
+  </si>
+  <si>
+    <t>Filling available excavated earth (excluding rock) in trenches, plinth, sides of foundations etc. in layers not exceeding 20 cm in depth, consolidating each deposited layer by ramming and watering, lead up to 50 m and lift up to 1.5 m as per DSR item  2.25</t>
+  </si>
+  <si>
+    <t>Inside Area of Basement</t>
+  </si>
+  <si>
+    <t>Cement concrete flooring 1:2:4 finished with a floating coat of neat cement, including cement slurry complete (40 mm thick with 20 mm nominal size stone aggregate) as per DSR item  11.3.1</t>
+  </si>
+  <si>
+    <t>Inside Area</t>
+  </si>
+  <si>
+    <t>Structural steel work  including wastage, cutting, hoisting, fixing in position and applying a priming coat of approved steel primer all complete as per DSR 10.1</t>
+  </si>
+  <si>
+    <t>MS angle 35 x 35 x 5mm</t>
+  </si>
+  <si>
+    <t>Total
+L</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Total Weight</t>
+  </si>
+  <si>
+    <t>Front side corner</t>
+  </si>
+  <si>
+    <t>Back side corner</t>
+  </si>
+  <si>
+    <t>Top edge front &amp; back</t>
+  </si>
+  <si>
+    <t>Top edge sides</t>
+  </si>
+  <si>
+    <t>Door vertical</t>
+  </si>
+  <si>
+    <t>Door Horizontal</t>
+  </si>
+  <si>
+    <t>Total Length</t>
+  </si>
+  <si>
+    <t>Kg/m</t>
+  </si>
+  <si>
+    <t>MS Flat 35 x 6mm</t>
+  </si>
+  <si>
+    <t>Back side  vertical</t>
+  </si>
+  <si>
+    <t>Back side Horizontal</t>
+  </si>
+  <si>
+    <t>Front side  vertical</t>
+  </si>
+  <si>
+    <t>Front side Horizontal</t>
+  </si>
+  <si>
+    <t>side  vertical</t>
+  </si>
+  <si>
+    <t>side Horizontal</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>GI Sheet work  including wastage, cutting, hoisting, fixing in position, welding and applying a priming coat of approved steel primer all complete</t>
+  </si>
+  <si>
+    <t>GI sheet 0.8 mm thick 8019</t>
+  </si>
+  <si>
+    <t>Front side</t>
+  </si>
+  <si>
+    <t>Back side</t>
+  </si>
+  <si>
+    <t>Sides</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>Total Area</t>
+  </si>
+  <si>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>Coursed rubble masonry (first sort) with hard stone in foundation and plinth with Cement mortar 1:6 as per DSR item 7.6.1</t>
-  </si>
-  <si>
-    <t>Foundation &amp; Basement</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>12 mm cement plaster of mix 1:4 as per DSR item 13.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outside </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top </t>
-  </si>
-  <si>
-    <t>Step sides</t>
-  </si>
-  <si>
-    <t>Step top</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>Filling available excavated earth (excluding rock) in trenches, plinth, sides of foundations etc. in layers not exceeding 20 cm in depth, consolidating each deposited layer by ramming and watering, lead up to 50 m and lift up to 1.5 m as per DSR item  2.25</t>
-  </si>
-  <si>
-    <t>Inside Area of Basement</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>Cement concrete flooring 1:2:4 finished with a floating coat of neat cement, including cement slurry complete (40 mm thick with 20 mm nominal size stone aggregate) as per DSR item  11.3.1</t>
-  </si>
-  <si>
-    <t>Inside Area</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>Structural steel work  including wastage, cutting, hoisting, fixing in position and applying a priming coat of approved steel primer all complete as per DSR 10.1</t>
-  </si>
-  <si>
-    <t>MS angle 35 x 35 x 5mm</t>
-  </si>
-  <si>
-    <t>Total
-L</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Total Weight</t>
-  </si>
-  <si>
-    <t>Front side corner</t>
-  </si>
-  <si>
-    <t>Back side corner</t>
-  </si>
-  <si>
-    <t>Top edge front &amp; back</t>
-  </si>
-  <si>
-    <t>Top edge sides</t>
-  </si>
-  <si>
-    <t>Door vertical</t>
-  </si>
-  <si>
-    <t>Door Horizontal</t>
-  </si>
-  <si>
-    <t>Total Length</t>
-  </si>
-  <si>
-    <t>Kg/m</t>
-  </si>
-  <si>
-    <t>MS Flat 35 x 6mm</t>
-  </si>
-  <si>
-    <t>Back side  vertical</t>
-  </si>
-  <si>
-    <t>Back side Horizontal</t>
-  </si>
-  <si>
-    <t>Front side  vertical</t>
-  </si>
-  <si>
-    <t>Front side Horizontal</t>
-  </si>
-  <si>
-    <t>side  vertical</t>
-  </si>
-  <si>
-    <t>side Horizontal</t>
-  </si>
-  <si>
-    <t>Roof</t>
-  </si>
-  <si>
-    <t>GI Sheet work  including wastage, cutting, hoisting, fixing in position, welding and applying a priming coat of approved steel primer all complete</t>
-  </si>
-  <si>
-    <t>GI sheet 0.8 mm thick 8019</t>
-  </si>
-  <si>
-    <t>Front side</t>
-  </si>
-  <si>
-    <t>Back side</t>
-  </si>
-  <si>
-    <t>Sides</t>
-  </si>
-  <si>
-    <t>roof</t>
-  </si>
-  <si>
-    <t>Total Area</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>Kg/m</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -362,40 +280,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00;[RED]0.00"/>
-    <numFmt numFmtId="165" formatCode="0.000;[RED]0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000;[RED]0.000"/>
+    <numFmt numFmtId="178" formatCode="0.00;[RED]0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font/>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="13"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -403,17 +338,23 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="8">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF3D3D3D"/>
@@ -438,11 +379,13 @@
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF3D3D3D"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -451,6 +394,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -465,6 +410,8 @@
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -473,11 +420,13 @@
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF3D3D3D"/>
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
@@ -489,138 +438,397 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="178" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HDPE Pipe PRICE"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -761,35 +969,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.0"/>
-    <col customWidth="1" min="2" max="2" width="39.88"/>
-    <col customWidth="1" min="3" max="3" width="4.13"/>
-    <col customWidth="1" min="4" max="4" width="7.88"/>
-    <col customWidth="1" min="5" max="5" width="6.0"/>
-    <col customWidth="1" min="6" max="6" width="7.88"/>
-    <col customWidth="1" min="7" max="7" width="9.38"/>
-    <col customWidth="1" min="8" max="8" width="7.88"/>
-    <col customWidth="1" min="9" max="9" width="8.25"/>
-    <col customWidth="1" min="10" max="10" width="10.38"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571F2E62-4951-4097-9AF7-81054B4AB9A6}">
+  <dimension ref="A1:J63"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -821,9 +1021,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="12.75">
       <c r="A3" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
@@ -837,22 +1037,22 @@
       <c r="I3" s="7"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="12.75">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="E4" s="10">
-        <v>1.5</v>
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.50</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f>PRODUCT(C4:F4)</f>
         <v>3</v>
       </c>
@@ -860,23 +1060,23 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13" t="s">
+    <row r="5" spans="1:10" ht="12.75">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <f>SUM(G4)</f>
         <v>3</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="2">
         <v>24.43</v>
       </c>
       <c r="J5" s="4">
@@ -884,11 +1084,11 @@
         <v>73.29</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="12.75">
       <c r="A6" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="7"/>
@@ -897,87 +1097,87 @@
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="15"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="12.75">
       <c r="A7" s="8"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
         <f>2*(1.2+0.9)</f>
-        <v>4.2</v>
+        <v>4.20</v>
       </c>
       <c r="E7" s="2">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="F7" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="11">
-        <f t="shared" ref="G7:G8" si="1">PRODUCT(C7:F7)</f>
+        <v>0.30</v>
+      </c>
+      <c r="G7" s="10">
+        <f>PRODUCT(C7:F7)</f>
         <v>0.378</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="12.75">
       <c r="A8" s="8"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="E8" s="2">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="F8" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="11">
-        <f t="shared" si="1"/>
+        <v>0.20</v>
+      </c>
+      <c r="G8" s="10">
+        <f>PRODUCT(C8:F8)</f>
         <v>0.03</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="1:10" ht="12.75">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <f>SUM(G7:G8)</f>
-        <v>0.408</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="2">
         <v>249.04</v>
       </c>
       <c r="J9" s="4">
         <f>G9*I9</f>
-        <v>101.60832</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>101.60832000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="12.75">
       <c r="A10" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>18</v>
@@ -988,93 +1188,93 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="15"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" ht="12.75">
       <c r="A11" s="8"/>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" ref="D11:E11" si="2">D7</f>
-        <v>4.2</v>
+        <f>D7</f>
+        <v>4.20</v>
       </c>
       <c r="E11" s="2">
-        <f t="shared" si="2"/>
-        <v>0.3</v>
+        <f>E7</f>
+        <v>0.30</v>
       </c>
       <c r="F11" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G11" s="11">
-        <f t="shared" ref="G11:G12" si="4">PRODUCT(C11:F11)</f>
+        <v>0.10</v>
+      </c>
+      <c r="G11" s="10">
+        <f>PRODUCT(C11:F11)</f>
         <v>0.126</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="12.75">
       <c r="A12" s="8"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" ref="D12:E12" si="3">D8</f>
-        <v>0.5</v>
+        <f>D8</f>
+        <v>0.50</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" si="3"/>
-        <v>0.3</v>
+        <f>E8</f>
+        <v>0.30</v>
       </c>
       <c r="F12" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G12" s="11">
-        <f t="shared" si="4"/>
+        <v>0.10</v>
+      </c>
+      <c r="G12" s="10">
+        <f>PRODUCT(C12:F12)</f>
         <v>0.015</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13" t="s">
+    <row r="13" spans="1:10" ht="12.75">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <f>SUM(G11:G12)</f>
-        <v>0.141</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="10">
+        <v>17</v>
+      </c>
+      <c r="I13" s="2">
         <v>5491.79</v>
       </c>
       <c r="J13" s="4">
         <f>G13*I13</f>
-        <v>774.34239</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>774.34239000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="12.75">
       <c r="A14" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1085,92 +1285,92 @@
       <c r="I14" s="7"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" ht="12.75">
       <c r="A15" s="8"/>
-      <c r="B15" s="16" t="s">
-        <v>21</v>
+      <c r="B15" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="C15" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" ref="D15:E15" si="5">D11</f>
-        <v>4.2</v>
+        <f>D11</f>
+        <v>4.20</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="5"/>
-        <v>0.3</v>
+        <f>E11</f>
+        <v>0.30</v>
       </c>
       <c r="F15" s="2">
         <f>0.2+0.3</f>
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="11">
-        <f t="shared" ref="G15:G16" si="7">PRODUCT(C15:F15)</f>
+        <v>0.50</v>
+      </c>
+      <c r="G15" s="10">
+        <f>PRODUCT(C15:F15)</f>
         <v>0.63</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" ht="12.75">
       <c r="A16" s="8"/>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" ref="D16:E16" si="6">D12</f>
-        <v>0.5</v>
+        <f>D12</f>
+        <v>0.50</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="6"/>
-        <v>0.3</v>
+        <f>E12</f>
+        <v>0.30</v>
       </c>
       <c r="F16" s="2">
         <f>0.1+0.15</f>
         <v>0.25</v>
       </c>
-      <c r="G16" s="11">
-        <f t="shared" si="7"/>
+      <c r="G16" s="10">
+        <f>PRODUCT(C16:F16)</f>
         <v>0.0375</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13" t="s">
+    <row r="17" spans="1:10" ht="12.75">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <f>SUM(G15:G16)</f>
         <v>0.6675</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="10">
+        <v>17</v>
+      </c>
+      <c r="I17" s="2">
         <v>6870.79</v>
       </c>
       <c r="J17" s="4">
         <f>G17*I17</f>
-        <v>4586.252325</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>4586.2523250000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="12.75">
       <c r="A18" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -1181,132 +1381,132 @@
       <c r="I18" s="7"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" ht="12.75">
       <c r="A19" s="8"/>
-      <c r="B19" s="13" t="s">
-        <v>24</v>
+      <c r="B19" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="C19" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
         <f>2*(1.2+0.3+0.9+0.3)</f>
-        <v>5.4</v>
-      </c>
-      <c r="E19" s="17"/>
+        <v>5.40</v>
+      </c>
+      <c r="E19" s="15"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="11">
-        <f t="shared" ref="G19:G22" si="9">PRODUCT(C19:F19)</f>
-        <v>5.4</v>
+      <c r="G19" s="10">
+        <f>PRODUCT(C19:F19)</f>
+        <v>5.40</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" ht="12.75">
       <c r="A20" s="8"/>
-      <c r="B20" s="13" t="s">
-        <v>25</v>
+      <c r="B20" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="C20" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" ref="D20:E20" si="8">D15</f>
-        <v>4.2</v>
+        <f>D15</f>
+        <v>4.20</v>
       </c>
       <c r="E20" s="2">
-        <f t="shared" si="8"/>
-        <v>0.3</v>
+        <f>E15</f>
+        <v>0.30</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="11">
-        <f t="shared" si="9"/>
+      <c r="G20" s="10">
+        <f>PRODUCT(C20:F20)</f>
         <v>1.26</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" ht="12.75">
       <c r="A21" s="8"/>
-      <c r="B21" s="13" t="s">
-        <v>26</v>
+      <c r="B21" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="C21" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2">
         <f>E12</f>
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="F21" s="2">
         <v>0.15</v>
       </c>
-      <c r="G21" s="11">
-        <f t="shared" si="9"/>
+      <c r="G21" s="10">
+        <f>PRODUCT(C21:F21)</f>
         <v>0.09</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" ht="12.75">
       <c r="A22" s="8"/>
-      <c r="B22" s="13" t="s">
-        <v>27</v>
+      <c r="B22" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="C22" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" ref="D22:E22" si="10">D16</f>
-        <v>0.5</v>
+        <f>D16</f>
+        <v>0.50</v>
       </c>
       <c r="E22" s="2">
-        <f t="shared" si="10"/>
-        <v>0.3</v>
+        <f>E16</f>
+        <v>0.30</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="11">
-        <f t="shared" si="9"/>
+      <c r="G22" s="10">
+        <f>PRODUCT(C22:F22)</f>
         <v>0.15</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13" t="s">
+    <row r="23" spans="1:10" ht="12.75">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="11">
+      <c r="G23" s="10">
         <f>SUM(G19:G22)</f>
-        <v>6.9</v>
+        <v>6.90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="10">
+        <v>13</v>
+      </c>
+      <c r="I23" s="2">
         <v>255.98</v>
       </c>
       <c r="J23" s="4">
         <f>G23*I23</f>
-        <v>1766.262</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>1766.2619999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="12.75">
       <c r="A24" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -1317,63 +1517,63 @@
       <c r="I24" s="7"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" ht="12.75">
       <c r="A25" s="8"/>
-      <c r="B25" s="19" t="s">
-        <v>30</v>
+      <c r="B25" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="C25" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2">
         <f>1.2-E15</f>
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="E25" s="2">
         <f>0.9-E15</f>
-        <v>0.6</v>
-      </c>
-      <c r="F25" s="10">
+        <v>0.60</v>
+      </c>
+      <c r="F25" s="2">
         <v>0.27</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="10">
         <f>PRODUCT(C25:F25)</f>
-        <v>0.1458</v>
+        <v>0.14580000000000001</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13" t="s">
+    <row r="26" spans="1:10" ht="12.75">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="11">
+      <c r="G26" s="10">
         <f>SUM(G25)</f>
-        <v>0.1458</v>
+        <v>0.14580000000000001</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="10">
+        <v>17</v>
+      </c>
+      <c r="I26" s="2">
         <v>220.47</v>
       </c>
       <c r="J26" s="4">
         <f>G26*I26</f>
-        <v>32.144526</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>32.144525999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="12.75">
       <c r="A27" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -1384,24 +1584,24 @@
       <c r="I27" s="7"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" ht="12.75">
       <c r="A28" s="8"/>
       <c r="B28" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C28" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" ref="D28:E28" si="11">D25</f>
-        <v>0.9</v>
+        <f>D25</f>
+        <v>0.90</v>
       </c>
       <c r="E28" s="2">
-        <f t="shared" si="11"/>
-        <v>0.6</v>
+        <f>E25</f>
+        <v>0.60</v>
       </c>
       <c r="F28" s="2"/>
-      <c r="G28" s="11">
+      <c r="G28" s="10">
         <f>PRODUCT(C28:F28)</f>
         <v>0.54</v>
       </c>
@@ -1409,23 +1609,23 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13" t="s">
+    <row r="29" spans="1:10" ht="12.75">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="11">
+      <c r="G29" s="10">
         <f>SUM(G27:G28)</f>
         <v>0.54</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="10">
+        <v>13</v>
+      </c>
+      <c r="I29" s="2">
         <v>473.11</v>
       </c>
       <c r="J29" s="4">
@@ -1433,12 +1633,12 @@
         <v>255.4794</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" ht="12.75">
       <c r="A30" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>35</v>
+        <v>8</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -1449,10 +1649,10 @@
       <c r="I30" s="7"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10" ht="12.75">
       <c r="A31" s="8"/>
-      <c r="B31" s="13" t="s">
-        <v>36</v>
+      <c r="B31" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1461,36 +1661,36 @@
         <v>4</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J31" s="2"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" ht="12.75">
       <c r="A32" s="8"/>
-      <c r="B32" s="13" t="s">
-        <v>41</v>
+      <c r="B32" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="C32" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
-        <v>2.1</v>
+        <v>2.10</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E37" si="12">C32*D32</f>
-        <v>4.2</v>
+        <f>C32*D32</f>
+        <v>4.20</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="3"/>
@@ -1498,20 +1698,20 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:10" ht="12.75">
       <c r="A33" s="8"/>
-      <c r="B33" s="13" t="s">
-        <v>42</v>
+      <c r="B33" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C33" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2">
-        <v>2.3</v>
+        <v>2.30</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="12"/>
-        <v>4.6</v>
+        <f>C33*D33</f>
+        <v>4.60</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="3"/>
@@ -1519,20 +1719,20 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" ht="12.75">
       <c r="A34" s="8"/>
-      <c r="B34" s="13" t="s">
-        <v>43</v>
+      <c r="B34" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="C34" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2">
-        <v>1.2</v>
+        <v>1.20</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="12"/>
-        <v>2.4</v>
+        <f>C34*D34</f>
+        <v>2.40</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="3"/>
@@ -1540,20 +1740,20 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:10" ht="12.75">
       <c r="A35" s="8"/>
-      <c r="B35" s="13" t="s">
-        <v>44</v>
+      <c r="B35" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C35" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D35" s="2">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="E35" s="2">
-        <f t="shared" si="12"/>
-        <v>1.8</v>
+        <f>C35*D35</f>
+        <v>1.80</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="3"/>
@@ -1561,20 +1761,20 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:10" ht="12.75">
       <c r="A36" s="8"/>
-      <c r="B36" s="13" t="s">
-        <v>45</v>
+      <c r="B36" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C36" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2">
-        <v>1.8</v>
+        <v>1.80</v>
       </c>
       <c r="E36" s="2">
-        <f t="shared" si="12"/>
-        <v>3.6</v>
+        <f>C36*D36</f>
+        <v>3.60</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="3"/>
@@ -1582,20 +1782,20 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:10" ht="12.75">
       <c r="A37" s="8"/>
-      <c r="B37" s="13" t="s">
-        <v>46</v>
+      <c r="B37" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C37" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2">
-        <v>0.6</v>
+        <v>0.60</v>
       </c>
       <c r="E37" s="2">
-        <f t="shared" si="12"/>
-        <v>1.2</v>
+        <f>C37*D37</f>
+        <v>1.20</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="3"/>
@@ -1603,39 +1803,39 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:10" ht="12.75">
       <c r="A38" s="8"/>
-      <c r="B38" s="13" t="s">
-        <v>47</v>
+      <c r="B38" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2">
         <f>SUM(E32:E37)</f>
-        <v>17.8</v>
+        <v>17.80</v>
       </c>
       <c r="F38" s="2">
-        <v>2.6</v>
+        <v>2.60</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H38" s="2">
         <f>E38*F38</f>
         <v>46.28</v>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="3">
         <v>80.78</v>
       </c>
       <c r="J38" s="4">
         <f>H38*I38</f>
-        <v>3738.4984</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>3738.4983999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="12.75">
       <c r="A39" s="8"/>
-      <c r="B39" s="13" t="s">
-        <v>49</v>
+      <c r="B39" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1646,20 +1846,20 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:10" ht="12.75">
       <c r="A40" s="8"/>
-      <c r="B40" s="13" t="s">
-        <v>50</v>
+      <c r="B40" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="C40" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2">
-        <v>2.3</v>
+        <v>2.30</v>
       </c>
       <c r="E40" s="2">
-        <f t="shared" ref="E40:E49" si="13">C40*D40</f>
-        <v>4.6</v>
+        <f>C40*D40</f>
+        <v>4.60</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="3"/>
@@ -1667,20 +1867,20 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:10" ht="12.75">
       <c r="A41" s="8"/>
-      <c r="B41" s="13" t="s">
-        <v>51</v>
+      <c r="B41" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C41" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2">
-        <v>1.2</v>
+        <v>1.20</v>
       </c>
       <c r="E41" s="2">
-        <f t="shared" si="13"/>
-        <v>2.4</v>
+        <f>C41*D41</f>
+        <v>2.40</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="3"/>
@@ -1688,20 +1888,20 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" ht="12.75">
       <c r="A42" s="8"/>
-      <c r="B42" s="13" t="s">
-        <v>52</v>
+      <c r="B42" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="C42" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2">
-        <v>2.1</v>
+        <v>2.10</v>
       </c>
       <c r="E42" s="2">
-        <f t="shared" si="13"/>
-        <v>2.1</v>
+        <f>C42*D42</f>
+        <v>2.10</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="3"/>
@@ -1709,20 +1909,20 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:10" ht="12.75">
       <c r="A43" s="8"/>
-      <c r="B43" s="13" t="s">
-        <v>53</v>
+      <c r="B43" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="C43" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2">
-        <v>0.6</v>
+        <v>0.60</v>
       </c>
       <c r="E43" s="2">
-        <f t="shared" si="13"/>
-        <v>1.2</v>
+        <f>C43*D43</f>
+        <v>1.20</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="3"/>
@@ -1730,20 +1930,20 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:10" ht="12.75">
       <c r="A44" s="8"/>
-      <c r="B44" s="13" t="s">
-        <v>54</v>
+      <c r="B44" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C44" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2">
-        <v>2.2</v>
+        <v>2.20</v>
       </c>
       <c r="E44" s="2">
-        <f t="shared" si="13"/>
-        <v>4.4</v>
+        <f>C44*D44</f>
+        <v>4.40</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="3"/>
@@ -1751,20 +1951,20 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:10" ht="12.75">
       <c r="A45" s="8"/>
-      <c r="B45" s="13" t="s">
-        <v>55</v>
+      <c r="B45" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="C45" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="E45" s="2">
-        <f t="shared" si="13"/>
-        <v>3.6</v>
+        <f>C45*D45</f>
+        <v>3.60</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="3"/>
@@ -1772,20 +1972,20 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:10" ht="12.75">
       <c r="A46" s="8"/>
-      <c r="B46" s="13" t="s">
-        <v>45</v>
+      <c r="B46" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C46" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>1.8</v>
+        <v>1.80</v>
       </c>
       <c r="E46" s="2">
-        <f t="shared" si="13"/>
-        <v>1.8</v>
+        <f>C46*D46</f>
+        <v>1.80</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="3"/>
@@ -1793,20 +1993,20 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:10" ht="12.75">
       <c r="A47" s="8"/>
-      <c r="B47" s="13" t="s">
-        <v>46</v>
+      <c r="B47" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C47" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2">
-        <v>0.6</v>
+        <v>0.60</v>
       </c>
       <c r="E47" s="2">
-        <f t="shared" si="13"/>
-        <v>1.2</v>
+        <f>C47*D47</f>
+        <v>1.20</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="3"/>
@@ -1814,20 +2014,20 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:10" ht="12.75">
       <c r="A48" s="8"/>
-      <c r="B48" s="13" t="s">
-        <v>56</v>
+      <c r="B48" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="C48" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2">
-        <v>1.2</v>
+        <v>1.20</v>
       </c>
       <c r="E48" s="2">
-        <f t="shared" si="13"/>
-        <v>2.4</v>
+        <f>C48*D48</f>
+        <v>2.40</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="3"/>
@@ -1835,18 +2035,18 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:10" ht="12.75">
       <c r="A49" s="8"/>
-      <c r="B49" s="13"/>
+      <c r="B49" s="12"/>
       <c r="C49" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="E49" s="2">
-        <f t="shared" si="13"/>
-        <v>0.9</v>
+        <f>C49*D49</f>
+        <v>0.90</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="3"/>
@@ -1854,41 +2054,41 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
     </row>
-    <row r="50">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13" t="s">
-        <v>47</v>
+    <row r="50" spans="1:10" ht="12.75">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2">
         <f>SUM(E40:E49)</f>
-        <v>24.6</v>
+        <v>24.60</v>
       </c>
       <c r="F50" s="2">
         <v>1.68</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H50" s="4">
         <f>E50*F50</f>
-        <v>41.328</v>
-      </c>
-      <c r="I50" s="20">
+        <v>41.328000000000003</v>
+      </c>
+      <c r="I50" s="3">
         <v>80.78</v>
       </c>
       <c r="J50" s="4">
         <f>H50*I50</f>
-        <v>3338.47584</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>3338.4758400000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="12.75">
       <c r="A51" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1899,10 +2099,10 @@
       <c r="I51" s="7"/>
       <c r="J51" s="2"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:10" ht="12.75">
       <c r="A52" s="8"/>
-      <c r="B52" s="16" t="s">
-        <v>58</v>
+      <c r="B52" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>4</v>
@@ -1917,20 +2117,20 @@
       <c r="I52" s="3"/>
       <c r="J52" s="2"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:10" ht="12.75">
       <c r="A53" s="8"/>
-      <c r="B53" s="13" t="s">
-        <v>59</v>
+      <c r="B53" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C53" s="2">
-        <v>1.2</v>
+        <v>1.20</v>
       </c>
       <c r="D53" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E53" s="2">
-        <f t="shared" ref="E53:E56" si="14">C53*D53</f>
-        <v>2.4</v>
+        <f>C53*D53</f>
+        <v>2.40</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -1938,19 +2138,19 @@
       <c r="I53" s="3"/>
       <c r="J53" s="2"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:10" ht="12.75">
       <c r="A54" s="8"/>
-      <c r="B54" s="13" t="s">
-        <v>60</v>
+      <c r="B54" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="C54" s="2">
-        <v>1.2</v>
+        <v>1.20</v>
       </c>
       <c r="D54" s="2">
-        <v>1.8</v>
+        <v>1.80</v>
       </c>
       <c r="E54" s="2">
-        <f t="shared" si="14"/>
+        <f>C54*D54</f>
         <v>2.16</v>
       </c>
       <c r="F54" s="2"/>
@@ -1959,19 +2159,19 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:10" ht="12.75">
       <c r="A55" s="8"/>
-      <c r="B55" s="13" t="s">
-        <v>61</v>
+      <c r="B55" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="C55" s="2">
-        <v>1.8</v>
+        <v>1.80</v>
       </c>
       <c r="D55" s="2">
-        <v>1.9</v>
+        <v>1.90</v>
       </c>
       <c r="E55" s="2">
-        <f t="shared" si="14"/>
+        <f>C55*D55</f>
         <v>3.42</v>
       </c>
       <c r="F55" s="2"/>
@@ -1980,19 +2180,19 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:10" ht="12.75">
       <c r="A56" s="8"/>
-      <c r="B56" s="13" t="s">
-        <v>62</v>
+      <c r="B56" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="C56" s="2">
-        <v>1.6</v>
+        <v>1.60</v>
       </c>
       <c r="D56" s="2">
-        <v>1.3</v>
+        <v>1.30</v>
       </c>
       <c r="E56" s="2">
-        <f t="shared" si="14"/>
+        <f>C56*D56</f>
         <v>2.08</v>
       </c>
       <c r="F56" s="2"/>
@@ -2001,10 +2201,10 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:10" ht="12.75">
       <c r="A57" s="8"/>
-      <c r="B57" s="13" t="s">
-        <v>63</v>
+      <c r="B57" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2013,10 +2213,10 @@
         <v>10.06</v>
       </c>
       <c r="F57" s="2">
-        <v>6.3</v>
+        <v>6.30</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H57" s="4">
         <f>E57*F57</f>
@@ -2025,9 +2225,9 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
-    <row r="58">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13" t="s">
+    <row r="58" spans="1:10" ht="12.75">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2"/>
@@ -2038,73 +2238,73 @@
         <v>63.38</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I58" s="20" t="str">
-        <f>'GI Works'!F29</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J58" s="4" t="str">
-        <f t="shared" ref="J58:J60" si="15">G58*I58</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>60</v>
+      </c>
+      <c r="I58" s="3">
+        <f>'[1]GI Works'!F29</f>
+        <v>151.03995699999999</v>
+      </c>
+      <c r="J58" s="4">
+        <f>G58*I58</f>
+        <v>9572.9124759999995</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="12.75">
       <c r="A59" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="B59" s="21" t="s">
-        <v>66</v>
+        <v>10</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I59" s="10">
+      <c r="G59" s="2">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" s="2">
         <v>222.08</v>
       </c>
       <c r="J59" s="2">
-        <f t="shared" si="15"/>
+        <f>G59*I59</f>
         <v>222.08</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:10" ht="12.75">
       <c r="A60" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>68</v>
+        <v>11</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I60" s="10">
+        <v>62</v>
+      </c>
+      <c r="I60" s="2">
         <v>128.23</v>
       </c>
       <c r="J60" s="4">
-        <f t="shared" si="15"/>
+        <f>G60*I60</f>
         <v>384.69</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10">
-        <v>12.0</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>69</v>
+    <row r="61" spans="1:10" ht="12.75">
+      <c r="A61" s="2">
+        <v>12</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -2112,17 +2312,17 @@
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="10">
+      <c r="I61" s="14"/>
+      <c r="J61" s="2">
         <v>1153.96</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="10">
-        <v>13.0</v>
-      </c>
-      <c r="B62" s="22" t="s">
-        <v>70</v>
+    <row r="62" spans="1:10" ht="12.75">
+      <c r="A62" s="2">
+        <v>13</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -2130,18 +2330,18 @@
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="23" t="str">
+      <c r="I62" s="14"/>
+      <c r="J62" s="17">
         <f>SUM(J5:J61)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="10">
-        <v>14.0</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>71</v>
+        <v>25999.99568</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="12.75">
+      <c r="A63" s="2">
+        <v>14</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>66</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -2150,7 +2350,7 @@
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
-      <c r="J63" s="15"/>
+      <c r="J63" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2177,9 +2377,6 @@
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B27:I27"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GWD Data/Metallic PH.xlsx
+++ b/GWD Data/Metallic PH.xlsx
@@ -604,6 +604,7 @@
       <sheetName val="GWD DR Abstract"/>
       <sheetName val="GWD MR Abstract"/>
       <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
       <sheetName val="BW Casing Pipes"/>
       <sheetName val="GI on Wall PRICE"/>
       <sheetName val="GI wo Trench"/>
@@ -679,6 +680,7 @@
       <sheetData sheetId="35"/>
       <sheetData sheetId="36"/>
       <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -980,7 +982,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571F2E62-4951-4097-9AF7-81054B4AB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FBAABE-EBD2-45CA-B8F1-F604A95CB9A6}">
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Metallic PH.xlsx
+++ b/GWD Data/Metallic PH.xlsx
@@ -627,6 +627,7 @@
       <sheetName val="Pump Pullout"/>
       <sheetName val="PVC Fittings"/>
       <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
       <sheetName val="PVC wo Trench"/>
       <sheetName val="PVC With Trench"/>
@@ -681,6 +682,7 @@
       <sheetData sheetId="36"/>
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -982,7 +984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FBAABE-EBD2-45CA-B8F1-F604A95CB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBF5B9F-5462-4819-A859-52B9D582B9A6}">
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
